--- a/results/Int Task Remove ACC 0.1/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_2_permute.xlsx
@@ -440,287 +440,287 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6947520061245169</v>
+        <v>0.7039051668949027</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6947520061245169</v>
+        <v>0.6973460830528585</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6880518015903636</v>
+        <v>0.693009195860379</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7161496581911477</v>
+        <v>0.6920504230895257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.711958434202326</v>
+        <v>0.6656953767528795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7114566380932595</v>
+        <v>0.6648777246741353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7068150997929221</v>
+        <v>0.6602473912356177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7072944861783488</v>
+        <v>0.6736926197512036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7076215470098464</v>
+        <v>0.6679287782642639</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7076215470098464</v>
+        <v>0.6669521382813195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6957668032044694</v>
+        <v>0.6669521382813195</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6936857272470138</v>
+        <v>0.6509240376992118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7066179547917137</v>
+        <v>0.6513810143609988</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.694503379325758</v>
+        <v>0.6738046683694019</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.694503379325758</v>
+        <v>0.693808980727032</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.694503379325758</v>
+        <v>0.6933295943416053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.679174219853925</v>
+        <v>0.6644477002475366</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6801217877629584</v>
+        <v>0.673251390462785</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6775613254200763</v>
+        <v>0.70254998428291</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.67419441586027</v>
+        <v>0.7209347398564203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6750232728008339</v>
+        <v>0.7318307108909441</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6748933569705445</v>
+        <v>0.7236251180295917</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6728571004603684</v>
+        <v>0.7185602176529267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6670641868995177</v>
+        <v>0.7085715375917057</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6619253950016626</v>
+        <v>0.7102292514728337</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6770349997486478</v>
+        <v>0.6790064497607308</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6768714693328989</v>
+        <v>0.6790064497607308</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6768714693328989</v>
+        <v>0.6783747378213751</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.650476146060522</v>
+        <v>0.676575903248138</v>
       </c>
     </row>
     <row r="31">
@@ -730,597 +730,597 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6384512094891249</v>
+        <v>0.6798755836370255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6155145545098357</v>
+        <v>0.6778393271268492</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6292084098241806</v>
+        <v>0.6613073105969527</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6053802112449571</v>
+        <v>0.6457340668379092</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5905349806700992</v>
+        <v>0.6476628172414357</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5772599449205333</v>
+        <v>0.6450508731010031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5610571090608569</v>
+        <v>0.6200219373024386</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5251636969745056</v>
+        <v>0.6229206653386381</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5103811530590181</v>
+        <v>0.583055583988313</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5103811530590181</v>
+        <v>0.5638692265435303</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5103811530590181</v>
+        <v>0.5656971331906783</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5311134786008338</v>
+        <v>0.526936184980761</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5378136831349871</v>
+        <v>0.5280718128679056</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5297716206893837</v>
+        <v>0.5294136707793556</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5284969919488525</v>
+        <v>0.5500430327260702</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5188532399312203</v>
+        <v>0.5760464886688563</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4874311733791865</v>
+        <v>0.5777108649002556</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4972675278864784</v>
+        <v>0.5618375125449027</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4949042105448046</v>
+        <v>0.5461319302827441</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4790799173141765</v>
+        <v>0.5467636422220997</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4792322428681055</v>
+        <v>0.5587794937703996</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4838961908920826</v>
+        <v>0.5570948276540835</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5091828385125031</v>
+        <v>0.6041149703616264</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4857734594980585</v>
+        <v>0.5995070466467483</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4857734594980585</v>
+        <v>0.6023385455120289</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4797452438389916</v>
+        <v>0.5500024529562363</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4473731867050983</v>
+        <v>0.5522179872555296</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.434597827225876</v>
+        <v>0.5761558117801255</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4585871335480225</v>
+        <v>0.4773259021882187</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4595168342449649</v>
+        <v>0.4581907237068832</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.456640515932405</v>
+        <v>0.4550097542864653</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4858606757197912</v>
+        <v>0.4567525645506033</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4894359351426258</v>
+        <v>0.4637013958835154</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4725989646707678</v>
+        <v>0.4637013958835154</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4716626016235542</v>
+        <v>0.5097491382855592</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4488470802855605</v>
+        <v>0.4997828679479779</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4643912519706929</v>
+        <v>0.5007192309951916</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4621466455974886</v>
+        <v>0.5007192309951916</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4332514268028774</v>
+        <v>0.5000987239176558</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4187444619213371</v>
+        <v>0.4923658550914589</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4487686462528216</v>
+        <v>0.4954393184052271</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.483118512914966</v>
+        <v>0.4954393184052271</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4666873401414477</v>
+        <v>0.4757981041373801</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4245149657585479</v>
+        <v>0.4756345737216313</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4008079008206198</v>
+        <v>0.5065188069063135</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4996550719564113</v>
+        <v>0.506028215659067</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4962993672584247</v>
+        <v>0.50843635244802</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4969758986450596</v>
+        <v>0.5055488292736403</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4966264280899224</v>
+        <v>0.5043929115015786</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5019175455417066</v>
+        <v>0.5064403728735747</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5016016895720288</v>
+        <v>0.5067562288432524</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5016016895720288</v>
+        <v>0.5016128944338486</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5009587727708533</v>
+        <v>0.5059385767645083</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5009699776326731</v>
+        <v>0.501285833602351</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4995318184763932</v>
+        <v>0.5107772600660542</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5006429168011755</v>
+        <v>0.5075850857838164</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5006429168011755</v>
+        <v>0.5080644721692431</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5006429168011755</v>
+        <v>0.5116285267302578</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5006429168011755</v>
+        <v>0.5055488292736403</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5006429168011755</v>
+        <v>0.502000522085994</v>
       </c>
     </row>
   </sheetData>
